--- a/begunici/app_types/animals/excel_templates/korm_plan.xlsx
+++ b/begunici/app_types/animals/excel_templates/korm_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D77D028-0A9F-4800-A53D-A7A9A564B5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D7FB7C-B827-487B-A29B-E2D8D10A97EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t xml:space="preserve">Кормовой план </t>
   </si>
@@ -85,24 +85,6 @@
     <t>2026 г.</t>
   </si>
   <si>
-    <t>Баранчики и ярки питомник ( от 3 до 6 мес)</t>
-  </si>
-  <si>
-    <t>Баран- производитель</t>
-  </si>
-  <si>
-    <t>Овцематки ярки ремонтные ( осемененные)</t>
-  </si>
-  <si>
-    <t>Овцематки с ягнятами</t>
-  </si>
-  <si>
-    <t>Баранчики, ярки   ремонтные (7-12 мес)</t>
-  </si>
-  <si>
-    <t>Приплод бараны и ярки ( до 3 мес)</t>
-  </si>
-  <si>
     <t>Итого на месяц</t>
   </si>
   <si>
@@ -110,6 +92,30 @@
   </si>
   <si>
     <t xml:space="preserve">     на </t>
+  </si>
+  <si>
+    <t>Баран-производитель</t>
+  </si>
+  <si>
+    <t>Овцематки, ярки (осемененные)</t>
+  </si>
+  <si>
+    <t>Овцематки с ягнятами (объягненные)</t>
+  </si>
+  <si>
+    <t>Баранчики и ярки питомник (от 3 до 6 мес)</t>
+  </si>
+  <si>
+    <t>Баранчики, ярки ремонтные (7-12 мес)</t>
+  </si>
+  <si>
+    <t>Приплод бараны и ярки (до 3 мес)</t>
+  </si>
+  <si>
+    <t>Баранчики (12+ мес)</t>
+  </si>
+  <si>
+    <t>Овцематки (неосемененные)</t>
   </si>
 </sst>
 </file>
@@ -1743,7 +1749,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1785,9 +1791,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2570,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2635,71 +2638,71 @@
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="21" t="s">
+      <c r="F6" s="24"/>
+      <c r="G6" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="21" t="s">
+      <c r="J6" s="21"/>
+      <c r="K6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="25"/>
-      <c r="O6" s="21" t="s">
+      <c r="N6" s="24"/>
+      <c r="O6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="20" t="s">
+      <c r="P6" s="24"/>
+      <c r="Q6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R6" s="20"/>
+      <c r="R6" s="19"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
     </row>
     <row r="8" spans="1:18" ht="30.4">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="28"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="9" t="s">
         <v>13</v>
       </c>
@@ -2744,11 +2747,11 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="28"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="11" t="s">
         <v>17</v>
       </c>
@@ -2793,7 +2796,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -2840,23 +2843,23 @@
         <v>0.01</v>
       </c>
       <c r="R10" s="15">
-        <f t="shared" ref="R10:R15" si="2">Q10*B10*C10</f>
+        <f t="shared" ref="R10:R17" si="2">Q10*B10*C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="15">
-        <f t="shared" ref="D11:D15" si="3">B11*C11</f>
+        <f t="shared" ref="D11:D17" si="3">B11*C11</f>
         <v>0</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="15">
-        <f t="shared" ref="F11:F15" si="4">B11*E11*C11</f>
+        <f t="shared" ref="F11:F17" si="4">B11*E11*C11</f>
         <v>0</v>
       </c>
       <c r="G11" s="15"/>
@@ -2865,7 +2868,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" ref="J11:J15" si="5">B11*I11*C11</f>
+        <f t="shared" ref="J11:J17" si="5">B11*I11*C11</f>
         <v>0</v>
       </c>
       <c r="K11" s="14">
@@ -2879,14 +2882,14 @@
         <v>0.3</v>
       </c>
       <c r="N11" s="14">
-        <f t="shared" ref="N11:N15" si="7">B11*M11*C11</f>
+        <f t="shared" ref="N11:N17" si="7">B11*M11*C11</f>
         <v>0</v>
       </c>
       <c r="O11" s="16">
         <v>0.01</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" ref="P11:P15" si="8">B11*O11*C11</f>
+        <f t="shared" ref="P11:P17" si="8">B11*O11*C11</f>
         <v>0</v>
       </c>
       <c r="Q11" s="16">
@@ -2899,7 +2902,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -2952,7 +2955,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -2996,14 +2999,14 @@
       <c r="Q13" s="16">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="R13" s="19">
+      <c r="R13" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -3056,7 +3059,7 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3104,48 +3107,114 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="13"/>
+      <c r="A16" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
+      <c r="D16" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
+      <c r="F16" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="15"/>
+      <c r="I16" s="14">
+        <v>3</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" ref="L16:L17" si="9">B16*K16*C16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="P16" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
+      <c r="D17" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
+      <c r="I17" s="14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="N17" s="14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B18" s="14">
         <f>SUM(B10:B17)</f>
